--- a/examples/reports/Tomography_Report_Bell_State_Flexible_Backend.xlsx
+++ b/examples/reports/Tomography_Report_Bell_State_Flexible_Backend.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="4" t="n">
-        <v>0.9999445041474824</v>
+        <v>0.9999405233116132</v>
       </c>
       <c r="D8" s="4" t="n"/>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="4" t="n">
-        <v>0.7164306640624998</v>
+        <v>0.7187499999999998</v>
       </c>
       <c r="D9" s="4" t="n"/>
     </row>
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>4044</v>
+        <v>4028</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3967</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="3">
@@ -658,16 +658,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2022</v>
+        <v>2035</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2075</v>
+        <v>2027</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2045</v>
+        <v>2058</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2050</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="4">
@@ -677,16 +677,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2085</v>
+        <v>2045</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2036</v>
+        <v>2066</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2031</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="5">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2091</v>
+        <v>2058</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1932</v>
+        <v>1988</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2038</v>
+        <v>2074</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2131</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="6">
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3966</v>
+        <v>3884</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3989</v>
+        <v>4096</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2081</v>
+        <v>2089</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2088</v>
+        <v>2011</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2018</v>
+        <v>2053</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2005</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="8">
@@ -753,16 +753,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2056</v>
+        <v>2010</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2018</v>
+        <v>1961</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2026</v>
+        <v>2032</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2092</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="9">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2054</v>
+        <v>2073</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2034</v>
+        <v>2129</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2097</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="10">
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4022</v>
+        <v>4057</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4038</v>
+        <v>4012</v>
       </c>
     </row>
   </sheetData>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>0.49365234375</v>
+        <v>0.49169921875</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.01171875</v>
+        <v>0.0106201171875</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.0103759765625</v>
+        <v>0.010986328125</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.4842529296875</v>
+        <v>0.4866943359375</v>
       </c>
     </row>
     <row r="3">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.246826171875</v>
+        <v>0.2484130859375</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.2532958984375</v>
+        <v>0.2474365234375</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.2496337890625</v>
+        <v>0.251220703125</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.250244140625</v>
+        <v>0.2529296875</v>
       </c>
     </row>
     <row r="4">
@@ -896,16 +896,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.2545166015625</v>
+        <v>0.2496337890625</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.24853515625</v>
+        <v>0.252197265625</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.2490234375</v>
+        <v>0.248779296875</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.2479248046875</v>
+        <v>0.2493896484375</v>
       </c>
     </row>
     <row r="5">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.2552490234375</v>
+        <v>0.251220703125</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.23583984375</v>
+        <v>0.24267578125</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.248779296875</v>
+        <v>0.253173828125</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.2601318359375</v>
+        <v>0.2529296875</v>
       </c>
     </row>
     <row r="6">
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.0155029296875</v>
+        <v>0.01171875</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.484130859375</v>
+        <v>0.47412109375</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.4869384765625</v>
+        <v>0.5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.013427734375</v>
+        <v>0.01416015625</v>
       </c>
     </row>
     <row r="7">
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.2540283203125</v>
+        <v>0.2550048828125</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.2548828125</v>
+        <v>0.2454833984375</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.246337890625</v>
+        <v>0.2506103515625</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.2447509765625</v>
+        <v>0.2489013671875</v>
       </c>
     </row>
     <row r="8">
@@ -972,16 +972,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.2509765625</v>
+        <v>0.245361328125</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.246337890625</v>
+        <v>0.2393798828125</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.247314453125</v>
+        <v>0.248046875</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.25537109375</v>
+        <v>0.2672119140625</v>
       </c>
     </row>
     <row r="9">
@@ -991,16 +991,16 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.250732421875</v>
+        <v>0.2530517578125</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.248291015625</v>
+        <v>0.2598876953125</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.2449951171875</v>
+        <v>0.246826171875</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.2559814453125</v>
+        <v>0.240234375</v>
       </c>
     </row>
     <row r="10">
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.490966796875</v>
+        <v>0.4952392578125</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.0067138671875</v>
+        <v>0.0074462890625</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.0093994140625</v>
+        <v>0.007568359375</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.492919921875</v>
+        <v>0.48974609375</v>
       </c>
     </row>
   </sheetData>

--- a/examples/reports/Tomography_Report_Bell_State_Flexible_Backend.xlsx
+++ b/examples/reports/Tomography_Report_Bell_State_Flexible_Backend.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="4" t="n">
-        <v>0.9999405233116132</v>
+        <v>0.9999900509002376</v>
       </c>
       <c r="D8" s="4" t="n"/>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="4" t="n">
-        <v>0.7187499999999998</v>
+        <v>0.7165527343749998</v>
       </c>
       <c r="D9" s="4" t="n"/>
     </row>
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>4028</v>
+        <v>3966</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3987</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="3">
@@ -658,16 +658,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2035</v>
+        <v>2083</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2027</v>
+        <v>1979</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2058</v>
+        <v>2069</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2072</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="4">
@@ -677,16 +677,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2045</v>
+        <v>2109</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2066</v>
+        <v>2048</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2038</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2043</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="5">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2058</v>
+        <v>2002</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1988</v>
+        <v>2086</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2074</v>
+        <v>2027</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2072</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="6">
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3884</v>
+        <v>4005</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4096</v>
+        <v>3978</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2089</v>
+        <v>2034</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2011</v>
+        <v>2114</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2053</v>
+        <v>1986</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2039</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="8">
@@ -753,16 +753,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2010</v>
+        <v>2091</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1961</v>
+        <v>2033</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2032</v>
+        <v>2071</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2189</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="9">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2073</v>
+        <v>2107</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2129</v>
+        <v>2048</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1968</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="10">
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4057</v>
+        <v>3998</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4012</v>
+        <v>4046</v>
       </c>
     </row>
   </sheetData>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>0.49169921875</v>
+        <v>0.484130859375</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.0106201171875</v>
+        <v>0.0115966796875</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.010986328125</v>
+        <v>0.01171875</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.4866943359375</v>
+        <v>0.4925537109375</v>
       </c>
     </row>
     <row r="3">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.2484130859375</v>
+        <v>0.2542724609375</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.2474365234375</v>
+        <v>0.2415771484375</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.251220703125</v>
+        <v>0.2525634765625</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.2529296875</v>
+        <v>0.2515869140625</v>
       </c>
     </row>
     <row r="4">
@@ -896,16 +896,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.2496337890625</v>
+        <v>0.2574462890625</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.252197265625</v>
+        <v>0.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.248779296875</v>
+        <v>0.247314453125</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.2493896484375</v>
+        <v>0.2452392578125</v>
       </c>
     </row>
     <row r="5">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.251220703125</v>
+        <v>0.244384765625</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.24267578125</v>
+        <v>0.254638671875</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.253173828125</v>
+        <v>0.2474365234375</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.2529296875</v>
+        <v>0.2535400390625</v>
       </c>
     </row>
     <row r="6">
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.01171875</v>
+        <v>0.01220703125</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.47412109375</v>
+        <v>0.4888916015625</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.5</v>
+        <v>0.485595703125</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.01416015625</v>
+        <v>0.0133056640625</v>
       </c>
     </row>
     <row r="7">
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.2550048828125</v>
+        <v>0.248291015625</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.2454833984375</v>
+        <v>0.258056640625</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.2506103515625</v>
+        <v>0.242431640625</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.2489013671875</v>
+        <v>0.251220703125</v>
       </c>
     </row>
     <row r="8">
@@ -972,16 +972,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.245361328125</v>
+        <v>0.2552490234375</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.2393798828125</v>
+        <v>0.2481689453125</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.248046875</v>
+        <v>0.2528076171875</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.2672119140625</v>
+        <v>0.2437744140625</v>
       </c>
     </row>
     <row r="9">
@@ -991,16 +991,16 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.2530517578125</v>
+        <v>0.2572021484375</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.2598876953125</v>
+        <v>0.25</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.246826171875</v>
+        <v>0.24658203125</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.240234375</v>
+        <v>0.2462158203125</v>
       </c>
     </row>
     <row r="10">
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.4952392578125</v>
+        <v>0.488037109375</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.0074462890625</v>
+        <v>0.0086669921875</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.007568359375</v>
+        <v>0.0093994140625</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.48974609375</v>
+        <v>0.493896484375</v>
       </c>
     </row>
   </sheetData>
